--- a/giro_da_praça_ofertas - QUINTA E SEXTA.xlsx
+++ b/giro_da_praça_ofertas - QUINTA E SEXTA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F8F41C-CF8D-4F6C-956F-ADB3145FECE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771FB2DC-721C-46DD-9E3A-5DF18E675C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -278,7 +278,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,21 +298,31 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -356,7 +366,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -364,22 +374,26 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -682,924 +696,931 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="31.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.5703125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="73.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
         <v>229173</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="E2" s="7"/>
+      <c r="F2" s="8">
         <v>14.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="5">
         <v>100037</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="7">
+      <c r="E3" s="7"/>
+      <c r="F3" s="8">
         <v>15.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>335057</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="E4" s="7"/>
+      <c r="F4" s="8">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
         <v>298239</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="E5" s="7"/>
+      <c r="F5" s="8">
         <v>6.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="5">
         <v>279573</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7">
+      <c r="E6" s="7"/>
+      <c r="F6" s="8">
         <v>7.59</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="5">
         <v>106680</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="E7" s="7"/>
+      <c r="F7" s="8">
         <v>8.49</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="5">
         <v>331297</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="E9" s="7"/>
+      <c r="F9" s="8">
         <v>11.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="5">
         <v>101137</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7">
+      <c r="E10" s="7"/>
+      <c r="F10" s="8">
         <v>15.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="5">
         <v>101136</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7">
+      <c r="E11" s="7"/>
+      <c r="F11" s="8">
         <v>15.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>250013</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7">
+      <c r="E12" s="7"/>
+      <c r="F12" s="8">
         <v>4.99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="5">
         <v>318863</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="7">
+      <c r="E13" s="7"/>
+      <c r="F13" s="8">
         <v>5.39</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="5">
         <v>239682</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="7">
+      <c r="E14" s="7"/>
+      <c r="F14" s="8">
         <v>15.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="5">
         <v>181693</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="7">
+      <c r="E15" s="7"/>
+      <c r="F15" s="8">
         <v>26.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="5">
         <v>111378</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="7">
+      <c r="E16" s="7"/>
+      <c r="F16" s="8">
         <v>14.49</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="5">
         <v>166557</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="7">
+      <c r="E17" s="7"/>
+      <c r="F17" s="8">
         <v>4.8899999999999997</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="5">
         <v>115724</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="7">
+      <c r="E18" s="7"/>
+      <c r="F18" s="8">
         <v>2.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="5">
         <v>128939</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="7">
+      <c r="E19" s="7"/>
+      <c r="F19" s="8">
         <v>14.49</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="5">
         <v>111514</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="7">
+      <c r="E20" s="7"/>
+      <c r="F20" s="8">
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="5">
         <v>234316</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="7">
+      <c r="E21" s="7"/>
+      <c r="F21" s="8">
         <v>4.49</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="5">
         <v>100758</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="7">
+      <c r="E22" s="7"/>
+      <c r="F22" s="8">
         <v>27.99</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="5">
         <v>311627</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="7">
+      <c r="E23" s="7"/>
+      <c r="F23" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="5">
         <v>106854</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="8">
         <v>11.69</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="5">
         <v>112978</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="7">
+      <c r="E25" s="7"/>
+      <c r="F25" s="8">
         <v>2.99</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="5">
         <v>100027</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="7">
+      <c r="E26" s="7"/>
+      <c r="F26" s="8">
         <v>7.99</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="5">
         <v>166152</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="7">
+      <c r="E27" s="7"/>
+      <c r="F27" s="8">
         <v>3.39</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="5">
         <v>101130</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="7">
+      <c r="E28" s="7"/>
+      <c r="F28" s="8">
         <v>7.69</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="5">
         <v>155079</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="7">
+      <c r="E29" s="7"/>
+      <c r="F29" s="8">
         <v>3.39</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="5">
         <v>155080</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="7">
+      <c r="E30" s="7"/>
+      <c r="F30" s="8">
         <v>7.19</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="5">
         <v>142446</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="7">
+      <c r="E31" s="7"/>
+      <c r="F31" s="8">
         <v>5.99</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="5">
         <v>307145</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="7">
+      <c r="E32" s="7"/>
+      <c r="F32" s="8">
         <v>20.7</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="5">
         <v>328759</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="7">
+      <c r="E33" s="7"/>
+      <c r="F33" s="8">
         <v>2.99</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="5">
         <v>174584</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="7">
+      <c r="E34" s="7"/>
+      <c r="F34" s="8">
         <v>3.19</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="5">
         <v>100426</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="7">
+      <c r="E36" s="7"/>
+      <c r="F36" s="8">
         <v>3.79</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="5">
         <v>260657</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="7">
+      <c r="E37" s="7"/>
+      <c r="F37" s="8">
         <v>10.99</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="5">
         <v>100423</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E38" s="5"/>
-      <c r="F38" s="7">
+      <c r="E38" s="7"/>
+      <c r="F38" s="8">
         <v>2.89</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="5">
         <v>326954</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E39" s="5"/>
-      <c r="F39" s="7">
+      <c r="E39" s="7"/>
+      <c r="F39" s="8">
         <v>5.99</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="5">
         <v>261980</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="7">
+      <c r="E40" s="7"/>
+      <c r="F40" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="5">
         <v>286263</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E41" s="5"/>
-      <c r="F41" s="7">
+      <c r="E41" s="7"/>
+      <c r="F41" s="8">
         <v>5.49</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="5">
         <v>100373</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E42" s="5"/>
-      <c r="F42" s="7">
+      <c r="E42" s="7"/>
+      <c r="F42" s="8">
         <v>25.49</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="5">
         <v>104406</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="E44" s="5"/>
-      <c r="F44" s="7">
+      <c r="E44" s="7"/>
+      <c r="F44" s="8">
         <v>10.99</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="5">
         <v>102282</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="7">
+      <c r="E45" s="7"/>
+      <c r="F45" s="8">
         <v>8.7899999999999991</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="5">
         <v>102237</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E46" s="5"/>
-      <c r="F46" s="7">
+      <c r="E46" s="7"/>
+      <c r="F46" s="8">
         <v>22.99</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="5">
         <v>102149</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E47" s="5"/>
-      <c r="F47" s="7">
+      <c r="E47" s="7"/>
+      <c r="F47" s="8">
         <v>5.99</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="5">
         <v>184034</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="7">
+      <c r="E48" s="7"/>
+      <c r="F48" s="8">
         <v>4.99</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49" s="5">
         <v>244191</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E49" s="5"/>
-      <c r="F49" s="7">
+      <c r="E49" s="7"/>
+      <c r="F49" s="8">
         <v>6.79</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="5">
         <v>287369</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E50" s="5"/>
-      <c r="F50" s="7">
+      <c r="E50" s="7"/>
+      <c r="F50" s="8">
         <f>15*3.79</f>
         <v>56.85</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="5">
         <v>324556</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="E51" s="5"/>
-      <c r="F51" s="7">
+      <c r="E51" s="7"/>
+      <c r="F51" s="8">
         <f>15*2.89</f>
         <v>43.35</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C52" s="3">
+      <c r="C52" s="5">
         <v>102085</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E52" s="5"/>
-      <c r="F52" s="7">
+      <c r="E52" s="7"/>
+      <c r="F52" s="8">
         <v>12.99</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C53" s="3">
+      <c r="C53" s="5">
         <v>102077</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E53" s="5"/>
-      <c r="F53" s="7">
+      <c r="E53" s="7"/>
+      <c r="F53" s="8">
         <v>185.99</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="96" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;LGIRO DA PRAÇA - QUINTA E SEXTA&amp;C&amp;P - &amp;N</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>